--- a/business_forms/033_home_office_setup_checklist_form--business_forms.xlsx
+++ b/business_forms/033_home_office_setup_checklist_form--business_forms.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -803,8 +803,8 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="30" customWidth="1" min="1" max="1"/>
-    <col width="44" customWidth="1" min="2" max="2"/>
-    <col width="44" customWidth="1" min="3" max="3"/>
+    <col width="31" customWidth="1" min="2" max="2"/>
+    <col width="31" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -832,12 +832,12 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>{'label':_'desk_lamp'}</t>
+          <t>desk_lamp</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>{'label': 'Desk Lamp'}</t>
+          <t>Desk Lamp</t>
         </is>
       </c>
     </row>
@@ -849,12 +849,12 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>{'label':_'bookshelves'}</t>
+          <t>bookshelves</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>{'label': 'Bookshelves'}</t>
+          <t>Bookshelves</t>
         </is>
       </c>
     </row>
@@ -866,12 +866,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>{'label':_'pens'}</t>
+          <t>pens</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>{'label': 'Pens'}</t>
+          <t>Pens</t>
         </is>
       </c>
     </row>
@@ -883,12 +883,12 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>{'label':_'notebooks'}</t>
+          <t>notebooks</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>{'label': 'Notebooks'}</t>
+          <t>Notebooks</t>
         </is>
       </c>
     </row>
@@ -900,12 +900,12 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>{'label':_'pencils'}</t>
+          <t>pencils</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>{'label': 'Pencils'}</t>
+          <t>Pencils</t>
         </is>
       </c>
     </row>
@@ -917,12 +917,12 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>{'label':_'calendar'}</t>
+          <t>calendar</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>{'label': 'Calendar'}</t>
+          <t>Calendar</t>
         </is>
       </c>
     </row>
@@ -934,12 +934,12 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>{'label':_'binder'}</t>
+          <t>binder</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>{'label': 'Binder'}</t>
+          <t>Binder</t>
         </is>
       </c>
     </row>
@@ -951,12 +951,12 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>{'label':_'desk'}</t>
+          <t>desk</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>{'label': 'Desk'}</t>
+          <t>Desk</t>
         </is>
       </c>
     </row>
@@ -968,12 +968,12 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>{'label':_'chair'}</t>
+          <t>chair</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>{'label': 'Chair'}</t>
+          <t>Chair</t>
         </is>
       </c>
     </row>
@@ -985,12 +985,12 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>{'label':_'home_office'}</t>
+          <t>home_office</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>{'label': 'Home Office'}</t>
+          <t>Home Office</t>
         </is>
       </c>
     </row>
@@ -1002,12 +1002,12 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>{'label':_'dedicated_office'}</t>
+          <t>dedicated_office</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>{'label': 'Dedicated Office'}</t>
+          <t>Dedicated Office</t>
         </is>
       </c>
     </row>
@@ -1019,12 +1019,12 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>{'label':_'fire_extinguisher'}</t>
+          <t>fire_extinguisher</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>{'label': 'Fire Extinguisher'}</t>
+          <t>Fire Extinguisher</t>
         </is>
       </c>
     </row>
@@ -1036,12 +1036,12 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>{'label':_'first_aid_kit'}</t>
+          <t>first_aid_kit</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>{'label': 'First Aid Kit'}</t>
+          <t>First Aid Kit</t>
         </is>
       </c>
     </row>
@@ -1053,12 +1053,12 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>{'label':_'u_shaped_desk'}</t>
+          <t>u_shaped_desk</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>{'label': 'U Shaped Desk'}</t>
+          <t>U Shaped Desk</t>
         </is>
       </c>
     </row>
@@ -1070,12 +1070,12 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>{'label':_'l_shaped_desk'}</t>
+          <t>l_shaped_desk</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>{'label': 'L Shaped Desk'}</t>
+          <t>L Shaped Desk</t>
         </is>
       </c>
     </row>
@@ -1087,12 +1087,12 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>{'label':_'plants'}</t>
+          <t>plants</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>{'label': 'Plants'}</t>
+          <t>Plants</t>
         </is>
       </c>
     </row>
@@ -1104,12 +1104,12 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>{'label':_'rug'}</t>
+          <t>rug</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>{'label': 'Rug'}</t>
+          <t>Rug</t>
         </is>
       </c>
     </row>
@@ -1121,12 +1121,12 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>{'label':_'computer'}</t>
+          <t>computer</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>{'label': 'Computer'}</t>
+          <t>Computer</t>
         </is>
       </c>
     </row>
@@ -1138,12 +1138,12 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>{'label':_'paper_tray'}</t>
+          <t>paper_tray</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>{'label': 'Paper Tray'}</t>
+          <t>Paper Tray</t>
         </is>
       </c>
     </row>
@@ -1155,12 +1155,12 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>{'label':_'home_office_work_station'}</t>
+          <t>home_office_work_station</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>{'label': 'Home Office Work Station'}</t>
+          <t>Home Office Work Station</t>
         </is>
       </c>
     </row>
@@ -1172,12 +1172,12 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>{'label':_'dedicated_office_work_station'}</t>
+          <t>dedicated_office_work_station</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>{'label': 'Dedicated Office Work Station'}</t>
+          <t>Dedicated Office Work Station</t>
         </is>
       </c>
     </row>
@@ -1189,12 +1189,12 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>{'label':_'phone'}</t>
+          <t>phone</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>{'label': 'Phone'}</t>
+          <t>Phone</t>
         </is>
       </c>
     </row>
@@ -1206,12 +1206,12 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>{'label':_'internet_connection'}</t>
+          <t>internet_connection</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>{'label': 'Internet Connection'}</t>
+          <t>Internet Connection</t>
         </is>
       </c>
     </row>
@@ -1223,12 +1223,12 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>{'label':_'conference_room'}</t>
+          <t>conference_room</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>{'label': 'Conference Room'}</t>
+          <t>Conference Room</t>
         </is>
       </c>
     </row>
